--- a/product_selector_out/STM32F469-479.xlsx
+++ b/product_selector_out/STM32F469-479.xlsx
@@ -21962,7 +21962,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22050,7 +22050,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22138,7 +22138,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22314,7 +22314,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22402,7 +22402,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22490,7 +22490,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22666,7 +22666,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22754,7 +22754,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -22930,7 +22930,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23018,7 +23018,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23106,7 +23106,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23194,7 +23194,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23370,7 +23370,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23458,7 +23458,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23546,7 +23546,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23634,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23722,7 +23722,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23810,7 +23810,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23898,7 +23898,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -23986,7 +23986,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24074,7 +24074,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24162,7 +24162,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24250,7 +24250,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24338,7 +24338,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24426,7 +24426,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
@@ -24514,7 +24514,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the footnote qualifies the figure</t>
+          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F469-479.xlsx
+++ b/product_selector_out/STM32F469-479.xlsx
@@ -11875,9 +11875,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA12" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB12" s="8" t="inlineStr">
@@ -12212,9 +12212,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr">
@@ -12549,9 +12549,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB14" s="8" t="inlineStr">
@@ -12886,9 +12886,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB15" s="8" t="inlineStr">
@@ -13223,9 +13223,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB16" s="8" t="inlineStr">
@@ -13560,9 +13560,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB17" s="8" t="inlineStr">
@@ -13897,9 +13897,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -14234,9 +14234,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB19" s="8" t="inlineStr">
@@ -14571,9 +14571,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB20" s="8" t="inlineStr">
@@ -14908,9 +14908,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB21" s="8" t="inlineStr">
@@ -15245,9 +15245,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB22" s="8" t="inlineStr">
@@ -15582,9 +15582,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB23" s="8" t="inlineStr">
@@ -15919,9 +15919,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB24" s="8" t="inlineStr">
@@ -16256,9 +16256,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA25" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB25" s="8" t="inlineStr">
@@ -16593,9 +16593,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA26" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB26" s="8" t="inlineStr">
@@ -16930,9 +16930,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA27" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA27" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB27" s="8" t="inlineStr">
@@ -17267,9 +17267,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA28" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB28" s="8" t="inlineStr">
@@ -17604,9 +17604,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA29" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA29" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB29" s="8" t="inlineStr">
@@ -17941,9 +17941,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA30" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB30" s="8" t="inlineStr">
@@ -18278,9 +18278,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA31" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -18615,9 +18615,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA32" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA32" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB32" s="8" t="inlineStr">
@@ -18952,9 +18952,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA33" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA33" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB33" s="8" t="inlineStr">
@@ -19289,9 +19289,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA34" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA34" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB34" s="8" t="inlineStr">
@@ -19626,9 +19626,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA35" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA35" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB35" s="8" t="inlineStr">
@@ -19963,9 +19963,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA36" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA36" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB36" s="8" t="inlineStr">
@@ -20300,9 +20300,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA37" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA37" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB37" s="8" t="inlineStr">
@@ -20637,9 +20637,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA38" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA38" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB38" s="8" t="inlineStr">
@@ -20974,9 +20974,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA39" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA39" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB39" s="8" t="inlineStr">
@@ -21311,9 +21311,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA40" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA40" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB40" s="8" t="inlineStr">
@@ -21648,9 +21648,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA41" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AA41" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AB41" s="8" t="inlineStr">

--- a/product_selector_out/STM32F469-479.xlsx
+++ b/product_selector_out/STM32F469-479.xlsx
@@ -1496,7 +1496,7 @@
       </c>
       <c r="AD13" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE13" s="4" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="AM13" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN13" s="4" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="BO13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BO18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>LQPF144</t>
+          <t>LQFP 144 20x20x1.4 mm</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -4574,7 +4574,7 @@
       </c>
       <c r="AM22" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN22" s="4" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="BO22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BO23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="AD24" s="4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>159</t>
         </is>
       </c>
       <c r="AE24" s="4" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="BO24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="BO25" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>LQPF144</t>
+          <t>LQFP 144 20x20x1.4 mm</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="AM26" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN26" s="4" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="BO26" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6736,7 +6736,7 @@
       </c>
       <c r="BO28" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="AD30" s="4" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AE30" s="4" t="inlineStr">
@@ -7270,7 +7270,7 @@
       </c>
       <c r="AM30" s="4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN30" s="4" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="BO30" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="AD31" s="4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>159</t>
         </is>
       </c>
       <c r="AE31" s="4" t="inlineStr">
@@ -7747,7 +7747,7 @@
       </c>
       <c r="BO31" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -12097,14 +12097,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -12132,9 +12132,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
@@ -12147,9 +12147,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O13" s="8" t="inlineStr">
@@ -12167,14 +12167,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R13" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S13" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -12212,9 +12212,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB13" s="8" t="inlineStr">
@@ -12227,9 +12227,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE13" s="8" t="inlineStr">
@@ -12267,14 +12267,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN13" s="8" t="inlineStr">
@@ -12282,9 +12282,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO13" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP13" s="6" t="inlineStr">
@@ -12292,9 +12292,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ13" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR13" s="6" t="inlineStr">
@@ -12322,14 +12322,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW13" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY13" s="6" t="inlineStr">
@@ -12342,14 +12342,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB13" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC13" s="8" t="inlineStr">
@@ -12412,9 +12412,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -13782,14 +13782,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -13817,9 +13817,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
@@ -13832,9 +13832,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O18" s="8" t="inlineStr">
@@ -13852,14 +13852,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S18" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -13897,9 +13897,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB18" s="8" t="inlineStr">
@@ -13912,9 +13912,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE18" s="8" t="inlineStr">
@@ -13952,14 +13952,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN18" s="8" t="inlineStr">
@@ -13967,9 +13967,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO18" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP18" s="6" t="inlineStr">
@@ -13977,9 +13977,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ18" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR18" s="6" t="inlineStr">
@@ -14007,14 +14007,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW18" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY18" s="6" t="inlineStr">
@@ -14027,14 +14027,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB18" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC18" s="8" t="inlineStr">
@@ -14097,9 +14097,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15130,14 +15130,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -15180,9 +15180,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O22" s="8" t="inlineStr">
@@ -15200,14 +15200,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S22" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -15245,9 +15245,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB22" s="8" t="inlineStr">
@@ -15260,9 +15260,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE22" s="8" t="inlineStr">
@@ -15300,14 +15300,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN22" s="8" t="inlineStr">
@@ -15315,9 +15315,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP22" s="6" t="inlineStr">
@@ -15325,9 +15325,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR22" s="6" t="inlineStr">
@@ -15355,14 +15355,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY22" s="6" t="inlineStr">
@@ -15375,14 +15375,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB22" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC22" s="8" t="inlineStr">
@@ -15445,9 +15445,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15467,14 +15467,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -15517,9 +15517,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O23" s="8" t="inlineStr">
@@ -15537,14 +15537,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S23" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -15582,9 +15582,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB23" s="8" t="inlineStr">
@@ -15597,9 +15597,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE23" s="8" t="inlineStr">
@@ -15637,14 +15637,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN23" s="8" t="inlineStr">
@@ -15652,9 +15652,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP23" s="6" t="inlineStr">
@@ -15662,9 +15662,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR23" s="6" t="inlineStr">
@@ -15692,14 +15692,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY23" s="6" t="inlineStr">
@@ -15712,14 +15712,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB23" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC23" s="8" t="inlineStr">
@@ -15782,9 +15782,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -15804,14 +15804,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -15839,9 +15839,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="K24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
@@ -15854,9 +15854,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O24" s="8" t="inlineStr">
@@ -15874,14 +15874,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S24" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -15919,9 +15919,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB24" s="8" t="inlineStr">
@@ -15934,9 +15934,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE24" s="8" t="inlineStr">
@@ -15974,14 +15974,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN24" s="8" t="inlineStr">
@@ -15989,9 +15989,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP24" s="6" t="inlineStr">
@@ -15999,9 +15999,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR24" s="6" t="inlineStr">
@@ -16029,14 +16029,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY24" s="6" t="inlineStr">
@@ -16049,14 +16049,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB24" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC24" s="8" t="inlineStr">
@@ -16119,9 +16119,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16141,14 +16141,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
@@ -16191,9 +16191,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O25" s="8" t="inlineStr">
@@ -16211,14 +16211,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S25" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -16256,9 +16256,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB25" s="8" t="inlineStr">
@@ -16271,9 +16271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE25" s="8" t="inlineStr">
@@ -16311,14 +16311,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN25" s="8" t="inlineStr">
@@ -16326,9 +16326,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO25" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP25" s="6" t="inlineStr">
@@ -16336,9 +16336,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ25" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR25" s="6" t="inlineStr">
@@ -16366,14 +16366,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW25" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY25" s="6" t="inlineStr">
@@ -16386,14 +16386,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA25" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB25" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC25" s="8" t="inlineStr">
@@ -16456,9 +16456,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -16478,14 +16478,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
@@ -16528,9 +16528,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O26" s="8" t="inlineStr">
@@ -16548,14 +16548,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R26" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S26" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -16593,9 +16593,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB26" s="8" t="inlineStr">
@@ -16608,9 +16608,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE26" s="8" t="inlineStr">
@@ -16648,14 +16648,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN26" s="8" t="inlineStr">
@@ -16663,9 +16663,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO26" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP26" s="6" t="inlineStr">
@@ -16673,9 +16673,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ26" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR26" s="6" t="inlineStr">
@@ -16703,14 +16703,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW26" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY26" s="6" t="inlineStr">
@@ -16723,14 +16723,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA26" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB26" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC26" s="8" t="inlineStr">
@@ -16793,9 +16793,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17152,14 +17152,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
@@ -17187,9 +17187,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="K28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="K28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr">
@@ -17202,9 +17202,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O28" s="8" t="inlineStr">
@@ -17222,14 +17222,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R28" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S28" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T28" s="6" t="inlineStr">
@@ -17267,9 +17267,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB28" s="8" t="inlineStr">
@@ -17282,9 +17282,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE28" s="8" t="inlineStr">
@@ -17322,14 +17322,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN28" s="8" t="inlineStr">
@@ -17337,9 +17337,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP28" s="6" t="inlineStr">
@@ -17347,9 +17347,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR28" s="6" t="inlineStr">
@@ -17377,14 +17377,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY28" s="6" t="inlineStr">
@@ -17397,14 +17397,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA28" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB28" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB28" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC28" s="8" t="inlineStr">
@@ -17467,9 +17467,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO28" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -17826,14 +17826,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
@@ -17861,9 +17861,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="K30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr">
@@ -17876,9 +17876,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O30" s="8" t="inlineStr">
@@ -17896,14 +17896,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R30" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S30" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T30" s="6" t="inlineStr">
@@ -17941,9 +17941,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB30" s="8" t="inlineStr">
@@ -17956,9 +17956,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE30" s="8" t="inlineStr">
@@ -17996,14 +17996,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN30" s="8" t="inlineStr">
@@ -18011,9 +18011,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO30" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP30" s="6" t="inlineStr">
@@ -18021,9 +18021,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ30" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR30" s="6" t="inlineStr">
@@ -18051,14 +18051,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW30" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY30" s="6" t="inlineStr">
@@ -18071,14 +18071,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA30" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB30" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB30" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC30" s="8" t="inlineStr">
@@ -18141,9 +18141,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO30" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -18163,14 +18163,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="E31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
@@ -18198,9 +18198,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="K31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="K31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr">
@@ -18213,9 +18213,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="N31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="N31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="O31" s="8" t="inlineStr">
@@ -18233,14 +18233,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R31" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S31" s="9" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T31" s="6" t="inlineStr">
@@ -18278,9 +18278,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AA31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AA31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AB31" s="8" t="inlineStr">
@@ -18293,9 +18293,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AD31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AD31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AE31" s="8" t="inlineStr">
@@ -18333,14 +18333,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AL31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="AM31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AM31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AN31" s="8" t="inlineStr">
@@ -18348,9 +18348,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AO31" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AO31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AP31" s="6" t="inlineStr">
@@ -18358,9 +18358,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AQ31" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="AQ31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AR31" s="6" t="inlineStr">
@@ -18388,14 +18388,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AW31" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AX31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AW31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AX31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AY31" s="6" t="inlineStr">
@@ -18408,14 +18408,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BA31" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
-        </is>
-      </c>
-      <c r="BB31" s="10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="BA31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="BB31" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="BC31" s="8" t="inlineStr">
@@ -18478,9 +18478,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO31" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BO31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -21869,7 +21869,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D121"/>
+  <dimension ref="A1:D81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -21991,7 +21991,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -22006,14 +22006,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -22028,14 +22028,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -22057,7 +22057,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32F479ZG</t>
+          <t>STM32F469BG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -22079,7 +22079,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469AG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -22094,14 +22094,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469AG</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -22123,7 +22123,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469AG</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -22145,7 +22145,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32F469BG</t>
+          <t>STM32F469AG</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -22167,7 +22167,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F469AG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -22182,14 +22182,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F469AG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -22211,7 +22211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F469AG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -22233,7 +22233,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32F469AG</t>
+          <t>STM32F469NG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -22255,7 +22255,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -22277,7 +22277,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -22299,7 +22299,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -22321,7 +22321,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F469NG</t>
+          <t>STM32F469II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -22343,7 +22343,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F469II</t>
+          <t>STM32F469AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -22358,14 +22358,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32F469II</t>
+          <t>STM32F469AI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -22387,7 +22387,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32F469II</t>
+          <t>STM32F469AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -22409,7 +22409,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32F469II</t>
+          <t>STM32F469AI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -22431,7 +22431,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32F479VG</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -22446,14 +22446,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32F479VG</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -22468,14 +22468,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32F479VG</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -22497,7 +22497,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>STM32F479VG</t>
+          <t>STM32F469NI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -22519,7 +22519,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>STM32F469AI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -22541,7 +22541,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32F469AI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -22563,7 +22563,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32F469AI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -22585,7 +22585,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32F469AI</t>
+          <t>STM32F469ZE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -22607,7 +22607,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469VE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -22622,14 +22622,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469VE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -22651,7 +22651,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469VE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -22673,7 +22673,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32F469NI</t>
+          <t>STM32F469VE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -22695,7 +22695,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -22717,7 +22717,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -22739,7 +22739,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -22761,7 +22761,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32F469ZE</t>
+          <t>STM32F469AE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -22783,7 +22783,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -22798,14 +22798,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -22820,14 +22820,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -22849,7 +22849,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32F469ZG</t>
+          <t>STM32F479IG</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -22871,7 +22871,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32F469VG</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -22886,14 +22886,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32F469VG</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -22908,14 +22908,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32F469VG</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -22937,7 +22937,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32F469VG</t>
+          <t>STM32F479BG</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -22959,7 +22959,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -22974,14 +22974,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -23003,7 +23003,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -23025,7 +23025,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32F479NG</t>
+          <t>STM32F479AG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23047,7 +23047,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32F469VI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23062,14 +23062,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32F469VI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -23091,7 +23091,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32F469VI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -23113,7 +23113,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32F469VI</t>
+          <t>STM32F469NE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -23135,7 +23135,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -23150,14 +23150,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -23172,14 +23172,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -23201,7 +23201,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32F469ZI</t>
+          <t>STM32F479II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -23223,7 +23223,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32F469VE</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -23238,14 +23238,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32F469VE</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -23260,14 +23260,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
+          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32F469VE</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -23289,7 +23289,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32F469VE</t>
+          <t>STM32F479BI</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -23311,7 +23311,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32F479VI</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -23333,7 +23333,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32F479VI</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -23355,7 +23355,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32F479VI</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -23377,7 +23377,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32F479VI</t>
+          <t>STM32F479AI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -23399,7 +23399,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -23414,14 +23414,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -23443,7 +23443,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -23465,7 +23465,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32F469AE</t>
+          <t>STM32F469IE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -23487,7 +23487,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -23502,14 +23502,14 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -23524,14 +23524,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -23553,7 +23553,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32F479ZI</t>
+          <t>STM32F469BE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -23575,7 +23575,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -23590,14 +23590,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -23612,14 +23612,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
+          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -23641,7 +23641,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32F479NI</t>
+          <t>STM32F469BI</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -23655,886 +23655,6 @@
         </is>
       </c>
       <c r="D81" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>STM32F479IG</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>STM32F479IG</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>STM32F479IG</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>STM32F479IG</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>STM32F479BG</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>STM32F479BG</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>STM32F479BG</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>STM32F479BG</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>STM32F479AG</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>STM32F479AG</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>STM32F479AG</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>STM32F479AG</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>STM32F469NE</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>STM32F469NE</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>STM32F469NE</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>STM32F469NE</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>STM32F479II</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>STM32F479II</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>STM32F479II</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>STM32F479II</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>STM32F479BI</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides Ethernet=No, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F479xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>STM32F479AI</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>STM32F469IE</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>STM32F469BE</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides Ethernet=Yes, Parallel camera interface=Yes, SD/MMC=Yes; ST also lists SAI, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>USB Type</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F469xx features and peripheral counts decides USB OTG FS=Yes, USB OTG HS=Yes; ST also lists USB OTG FS + USB OTG FS/HS, which the table does not mention</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>Table 17. General operating conditions: V_DD min reads '1.7(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>STM32F469BI</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Operating Temperature (°C) max</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
         <is>
           <t>Ambient operating temperature: −40 to 85 °C / −40 to 105 °C Junction temperature: −40 to 105 °C / −40 to 125 °C (datasheet offers 3 grades; the ordering-code suffix selects one)</t>
         </is>

--- a/product_selector_out/STM32F469-479.xlsx
+++ b/product_selector_out/STM32F469-479.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO41"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.61328125" customWidth="1" min="1" max="1"/>
@@ -575,7 +575,8 @@
     <col width="21.765625" customWidth="1" min="64" max="64"/>
     <col width="18" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
-    <col width="52" customWidth="1" min="67" max="67"/>
+    <col width="18" customWidth="1" min="67" max="67"/>
+    <col width="52" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -913,6 +914,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1010,6 +1016,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1344,6 +1351,11 @@
       </c>
       <c r="BO12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -1684,6 +1696,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2018,6 +2035,11 @@
       </c>
       <c r="BO14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -2355,6 +2377,11 @@
       </c>
       <c r="BO15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -2692,6 +2719,11 @@
       </c>
       <c r="BO16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -3029,6 +3061,11 @@
       </c>
       <c r="BO17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -3369,6 +3406,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3703,6 +3745,11 @@
       </c>
       <c r="BO19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -4040,6 +4087,11 @@
       </c>
       <c r="BO20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -4377,6 +4429,11 @@
       </c>
       <c r="BO21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -4717,6 +4774,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5054,6 +5116,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5391,6 +5458,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -5728,6 +5800,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -6065,6 +6142,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -6399,6 +6481,11 @@
       </c>
       <c r="BO27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -6739,6 +6826,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -7073,6 +7165,11 @@
       </c>
       <c r="BO29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -7413,6 +7510,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
@@ -7750,6 +7852,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BP31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
@@ -8084,6 +8191,11 @@
       </c>
       <c r="BO32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
         </is>
       </c>
@@ -8421,6 +8533,11 @@
       </c>
       <c r="BO33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
         </is>
       </c>
@@ -8758,6 +8875,11 @@
       </c>
       <c r="BO34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
         </is>
       </c>
@@ -9095,6 +9217,11 @@
       </c>
       <c r="BO35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -9432,6 +9559,11 @@
       </c>
       <c r="BO36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
         </is>
       </c>
@@ -9769,6 +9901,11 @@
       </c>
       <c r="BO37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
         </is>
       </c>
@@ -10106,6 +10243,11 @@
       </c>
       <c r="BO38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f479ag.pdf</t>
         </is>
       </c>
@@ -10443,6 +10585,11 @@
       </c>
       <c r="BO39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -10780,6 +10927,11 @@
       </c>
       <c r="BO40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
@@ -11117,12 +11269,17 @@
       </c>
       <c r="BO41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BP41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f469ae.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="66">
+  <mergeCells count="67">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -11145,12 +11302,14 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="A9:BP9"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
+    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="BM10:BM11"/>
-    <mergeCell ref="BD10:BD11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -11165,9 +11324,8 @@
     <mergeCell ref="BH10:BH11"/>
     <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
-    <mergeCell ref="A9:BO9"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
@@ -11233,7 +11391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BO41"/>
+  <dimension ref="A1:BP41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -11303,6 +11461,7 @@
     <col width="16" customWidth="1" min="65" max="65"/>
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
+    <col width="16" customWidth="1" min="68" max="68"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11646,6 +11805,11 @@
         </is>
       </c>
       <c r="BO10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BP10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -11743,6 +11907,7 @@
       <c r="BM11" s="2" t="n"/>
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
+      <c r="BP11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -12075,7 +12240,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO12" s="6" t="inlineStr">
+      <c r="BO12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -12417,6 +12587,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -12749,7 +12924,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO14" s="6" t="inlineStr">
+      <c r="BO14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13086,7 +13266,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO15" s="6" t="inlineStr">
+      <c r="BO15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13423,7 +13608,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO16" s="6" t="inlineStr">
+      <c r="BO16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -13760,7 +13950,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO17" s="6" t="inlineStr">
+      <c r="BO17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14102,6 +14297,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -14434,7 +14634,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO19" s="6" t="inlineStr">
+      <c r="BO19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -14771,7 +14976,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO20" s="6" t="inlineStr">
+      <c r="BO20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15108,7 +15318,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO21" s="6" t="inlineStr">
+      <c r="BO21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -15450,6 +15665,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -15787,6 +16007,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -16124,6 +16349,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -16461,6 +16691,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
@@ -16798,6 +17033,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -17130,7 +17370,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO27" s="6" t="inlineStr">
+      <c r="BO27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17472,6 +17717,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -17804,7 +18054,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO29" s="6" t="inlineStr">
+      <c r="BO29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18146,6 +18401,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -18483,6 +18743,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BP31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -18815,7 +19080,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO32" s="6" t="inlineStr">
+      <c r="BO32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19152,7 +19422,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO33" s="6" t="inlineStr">
+      <c r="BO33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19489,7 +19764,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO34" s="6" t="inlineStr">
+      <c r="BO34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19826,7 +20106,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO35" s="6" t="inlineStr">
+      <c r="BO35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20163,7 +20448,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO36" s="6" t="inlineStr">
+      <c r="BO36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20500,7 +20790,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO37" s="6" t="inlineStr">
+      <c r="BO37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20837,7 +21132,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO38" s="6" t="inlineStr">
+      <c r="BO38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21174,7 +21474,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO39" s="6" t="inlineStr">
+      <c r="BO39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21511,7 +21816,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO40" s="6" t="inlineStr">
+      <c r="BO40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21848,7 +22158,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BO41" s="6" t="inlineStr">
+      <c r="BO41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BP41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21856,8 +22171,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BO9"/>
-    <mergeCell ref="A1:BO8"/>
+    <mergeCell ref="A1:BP8"/>
+    <mergeCell ref="A9:BP9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
